--- a/data/availability/projects/sodic/ogami.xlsx
+++ b/data/availability/projects/sodic/ogami.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Delivery Note</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -467,6 +472,11 @@
       <c r="E2" t="inlineStr">
         <is>
           <t>Updated inventory for ogami</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
     </row>
@@ -2462,7 +2472,6 @@
       <c r="G25" t="n">
         <v>309</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2519,7 +2528,6 @@
       <c r="G26" t="n">
         <v>309</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2576,7 +2584,6 @@
       <c r="G27" t="n">
         <v>253</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2633,7 +2640,6 @@
       <c r="G28" t="n">
         <v>309</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2690,7 +2696,6 @@
       <c r="G29" t="n">
         <v>309</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2747,7 +2752,6 @@
       <c r="G30" t="n">
         <v>253</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2804,7 +2808,6 @@
       <c r="G31" t="n">
         <v>309</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2861,7 +2864,6 @@
       <c r="G32" t="n">
         <v>309</v>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2918,7 +2920,6 @@
       <c r="G33" t="n">
         <v>253</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2975,7 +2976,6 @@
       <c r="G34" t="n">
         <v>309</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3032,7 +3032,6 @@
       <c r="G35" t="n">
         <v>309</v>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3089,7 +3088,6 @@
       <c r="G36" t="n">
         <v>309</v>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3146,7 +3144,6 @@
       <c r="G37" t="n">
         <v>253</v>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3203,7 +3200,6 @@
       <c r="G38" t="n">
         <v>253</v>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3260,7 +3256,6 @@
       <c r="G39" t="n">
         <v>309</v>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3317,7 +3312,6 @@
       <c r="G40" t="n">
         <v>309</v>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3374,7 +3368,6 @@
       <c r="G41" t="n">
         <v>253</v>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3431,7 +3424,6 @@
       <c r="G42" t="n">
         <v>253</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3488,7 +3480,6 @@
       <c r="G43" t="n">
         <v>309</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3545,7 +3536,6 @@
       <c r="G44" t="n">
         <v>253</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3602,7 +3592,6 @@
       <c r="G45" t="n">
         <v>253</v>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3659,7 +3648,6 @@
       <c r="G46" t="n">
         <v>309</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3716,7 +3704,6 @@
       <c r="G47" t="n">
         <v>309</v>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3773,7 +3760,6 @@
       <c r="G48" t="n">
         <v>253</v>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3830,7 +3816,6 @@
       <c r="G49" t="n">
         <v>253</v>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3887,7 +3872,6 @@
       <c r="G50" t="n">
         <v>253</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3944,7 +3928,6 @@
       <c r="G51" t="n">
         <v>309</v>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4001,7 +3984,6 @@
       <c r="G52" t="n">
         <v>253</v>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4058,7 +4040,6 @@
       <c r="G53" t="n">
         <v>253</v>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4115,7 +4096,6 @@
       <c r="G54" t="n">
         <v>309</v>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4172,7 +4152,6 @@
       <c r="G55" t="n">
         <v>309</v>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4229,7 +4208,6 @@
       <c r="G56" t="n">
         <v>309</v>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4286,7 +4264,6 @@
       <c r="G57" t="n">
         <v>309</v>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4343,7 +4320,6 @@
       <c r="G58" t="n">
         <v>189</v>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4400,7 +4376,6 @@
       <c r="G59" t="n">
         <v>189</v>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4457,7 +4432,6 @@
       <c r="G60" t="n">
         <v>189</v>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4514,7 +4488,6 @@
       <c r="G61" t="n">
         <v>189</v>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4571,7 +4544,6 @@
       <c r="G62" t="n">
         <v>189</v>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4628,7 +4600,6 @@
       <c r="G63" t="n">
         <v>189</v>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4685,7 +4656,6 @@
       <c r="G64" t="n">
         <v>189</v>
       </c>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4742,7 +4712,6 @@
       <c r="G65" t="n">
         <v>189</v>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4799,7 +4768,6 @@
       <c r="G66" t="n">
         <v>189</v>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4856,7 +4824,6 @@
       <c r="G67" t="n">
         <v>189</v>
       </c>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4913,7 +4880,6 @@
       <c r="G68" t="n">
         <v>189</v>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4970,7 +4936,6 @@
       <c r="G69" t="n">
         <v>189</v>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5027,7 +4992,6 @@
       <c r="G70" t="n">
         <v>189</v>
       </c>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5084,7 +5048,6 @@
       <c r="G71" t="n">
         <v>189</v>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5141,7 +5104,6 @@
       <c r="G72" t="n">
         <v>189</v>
       </c>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5198,7 +5160,6 @@
       <c r="G73" t="n">
         <v>189</v>
       </c>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5255,7 +5216,6 @@
       <c r="G74" t="n">
         <v>189</v>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5312,7 +5272,6 @@
       <c r="G75" t="n">
         <v>189</v>
       </c>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5369,7 +5328,6 @@
       <c r="G76" t="n">
         <v>253</v>
       </c>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5426,7 +5384,6 @@
       <c r="G77" t="n">
         <v>309</v>
       </c>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5483,7 +5440,6 @@
       <c r="G78" t="n">
         <v>268</v>
       </c>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5540,7 +5496,6 @@
       <c r="G79" t="n">
         <v>268</v>
       </c>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5597,7 +5552,6 @@
       <c r="G80" t="n">
         <v>226</v>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5654,7 +5608,6 @@
       <c r="G81" t="n">
         <v>268</v>
       </c>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5711,7 +5664,6 @@
       <c r="G82" t="n">
         <v>268</v>
       </c>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5890,7 +5842,6 @@
       <c r="G85" t="n">
         <v>226</v>
       </c>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5947,7 +5898,6 @@
       <c r="G86" t="n">
         <v>268</v>
       </c>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6004,7 +5954,6 @@
       <c r="G87" t="n">
         <v>268</v>
       </c>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6366,7 +6315,6 @@
       <c r="G93" t="n">
         <v>268</v>
       </c>
-      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6667,7 +6615,6 @@
       <c r="G98" t="n">
         <v>158</v>
       </c>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6724,7 +6671,6 @@
       <c r="G99" t="n">
         <v>226</v>
       </c>
-      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6781,7 +6727,6 @@
       <c r="G100" t="n">
         <v>232</v>
       </c>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6899,7 +6844,6 @@
       <c r="G102" t="n">
         <v>232</v>
       </c>
-      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6956,7 +6900,6 @@
       <c r="G103" t="n">
         <v>226</v>
       </c>
-      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7013,7 +6956,6 @@
       <c r="G104" t="n">
         <v>181</v>
       </c>
-      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7070,7 +7012,6 @@
       <c r="G105" t="n">
         <v>181</v>
       </c>
-      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7127,7 +7068,6 @@
       <c r="G106" t="n">
         <v>150</v>
       </c>
-      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7184,7 +7124,6 @@
       <c r="G107" t="n">
         <v>181</v>
       </c>
-      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7302,7 +7241,6 @@
       <c r="G109" t="n">
         <v>150</v>
       </c>
-      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7359,7 +7297,6 @@
       <c r="G110" t="n">
         <v>181</v>
       </c>
-      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7416,7 +7353,6 @@
       <c r="G111" t="n">
         <v>150</v>
       </c>
-      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7473,7 +7409,6 @@
       <c r="G112" t="n">
         <v>150</v>
       </c>
-      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7530,7 +7465,6 @@
       <c r="G113" t="n">
         <v>181</v>
       </c>
-      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7648,7 +7582,6 @@
       <c r="G115" t="n">
         <v>150</v>
       </c>
-      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7705,7 +7638,6 @@
       <c r="G116" t="n">
         <v>181</v>
       </c>
-      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7884,7 +7816,6 @@
       <c r="G119" t="n">
         <v>150</v>
       </c>
-      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7941,7 +7872,6 @@
       <c r="G120" t="n">
         <v>181</v>
       </c>
-      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8059,7 +7989,6 @@
       <c r="G122" t="n">
         <v>150</v>
       </c>
-      <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8116,7 +8045,6 @@
       <c r="G123" t="n">
         <v>181</v>
       </c>
-      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8234,7 +8162,6 @@
       <c r="G125" t="n">
         <v>150</v>
       </c>
-      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8291,7 +8218,6 @@
       <c r="G126" t="n">
         <v>181</v>
       </c>
-      <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8470,7 +8396,6 @@
       <c r="G129" t="n">
         <v>150</v>
       </c>
-      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8527,7 +8452,6 @@
       <c r="G130" t="n">
         <v>181</v>
       </c>
-      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8645,7 +8569,6 @@
       <c r="G132" t="n">
         <v>150</v>
       </c>
-      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8702,7 +8625,6 @@
       <c r="G133" t="n">
         <v>181</v>
       </c>
-      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8759,7 +8681,6 @@
       <c r="G134" t="n">
         <v>150</v>
       </c>
-      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8816,7 +8737,6 @@
       <c r="G135" t="n">
         <v>181</v>
       </c>
-      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8873,7 +8793,6 @@
       <c r="G136" t="n">
         <v>150</v>
       </c>
-      <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8930,7 +8849,6 @@
       <c r="G137" t="n">
         <v>150</v>
       </c>
-      <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8987,7 +8905,6 @@
       <c r="G138" t="n">
         <v>181</v>
       </c>
-      <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9044,7 +8961,6 @@
       <c r="G139" t="n">
         <v>150</v>
       </c>
-      <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9101,7 +9017,6 @@
       <c r="G140" t="n">
         <v>181</v>
       </c>
-      <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9219,7 +9134,6 @@
       <c r="G142" t="n">
         <v>150</v>
       </c>
-      <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9276,7 +9190,6 @@
       <c r="G143" t="n">
         <v>181</v>
       </c>
-      <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9333,7 +9246,6 @@
       <c r="G144" t="n">
         <v>150</v>
       </c>
-      <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9390,7 +9302,6 @@
       <c r="G145" t="n">
         <v>181</v>
       </c>
-      <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9508,7 +9419,6 @@
       <c r="G147" t="n">
         <v>181</v>
       </c>
-      <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9626,7 +9536,6 @@
       <c r="G149" t="n">
         <v>181</v>
       </c>
-      <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9683,7 +9592,6 @@
       <c r="G150" t="n">
         <v>181</v>
       </c>
-      <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9740,7 +9648,6 @@
       <c r="G151" t="n">
         <v>268</v>
       </c>
-      <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9797,7 +9704,6 @@
       <c r="G152" t="n">
         <v>268</v>
       </c>
-      <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9854,7 +9760,6 @@
       <c r="G153" t="n">
         <v>226</v>
       </c>
-      <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9911,7 +9816,6 @@
       <c r="G154" t="n">
         <v>226</v>
       </c>
-      <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9968,7 +9872,6 @@
       <c r="G155" t="n">
         <v>226</v>
       </c>
-      <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10025,7 +9928,6 @@
       <c r="G156" t="n">
         <v>226</v>
       </c>
-      <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10082,7 +9984,6 @@
       <c r="G157" t="n">
         <v>226</v>
       </c>
-      <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10139,7 +10040,6 @@
       <c r="G158" t="n">
         <v>181</v>
       </c>
-      <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10196,7 +10096,6 @@
       <c r="G159" t="n">
         <v>150</v>
       </c>
-      <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10253,7 +10152,6 @@
       <c r="G160" t="n">
         <v>181</v>
       </c>
-      <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10310,7 +10208,6 @@
       <c r="G161" t="n">
         <v>181</v>
       </c>
-      <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10367,7 +10264,6 @@
       <c r="G162" t="n">
         <v>150</v>
       </c>
-      <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10424,7 +10320,6 @@
       <c r="G163" t="n">
         <v>181</v>
       </c>
-      <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10481,7 +10376,6 @@
       <c r="G164" t="n">
         <v>181</v>
       </c>
-      <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10538,7 +10432,6 @@
       <c r="G165" t="n">
         <v>150</v>
       </c>
-      <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10595,7 +10488,6 @@
       <c r="G166" t="n">
         <v>181</v>
       </c>
-      <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10652,7 +10544,6 @@
       <c r="G167" t="n">
         <v>150</v>
       </c>
-      <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10709,7 +10600,6 @@
       <c r="G168" t="n">
         <v>181</v>
       </c>
-      <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10766,7 +10656,6 @@
       <c r="G169" t="n">
         <v>150</v>
       </c>
-      <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10823,7 +10712,6 @@
       <c r="G170" t="n">
         <v>181</v>
       </c>
-      <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10880,7 +10768,6 @@
       <c r="G171" t="n">
         <v>181</v>
       </c>
-      <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10937,7 +10824,6 @@
       <c r="G172" t="n">
         <v>150</v>
       </c>
-      <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10994,7 +10880,6 @@
       <c r="G173" t="n">
         <v>150</v>
       </c>
-      <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11051,7 +10936,6 @@
       <c r="G174" t="n">
         <v>181</v>
       </c>
-      <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11108,7 +10992,6 @@
       <c r="G175" t="n">
         <v>150</v>
       </c>
-      <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11165,7 +11048,6 @@
       <c r="G176" t="n">
         <v>136</v>
       </c>
-      <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11222,7 +11104,6 @@
       <c r="G177" t="n">
         <v>136</v>
       </c>
-      <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11279,7 +11160,6 @@
       <c r="G178" t="n">
         <v>144</v>
       </c>
-      <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11336,7 +11216,6 @@
       <c r="G179" t="n">
         <v>144</v>
       </c>
-      <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11393,7 +11272,6 @@
       <c r="G180" t="n">
         <v>137</v>
       </c>
-      <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11450,7 +11328,6 @@
       <c r="G181" t="n">
         <v>123</v>
       </c>
-      <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11507,7 +11384,6 @@
       <c r="G182" t="n">
         <v>123</v>
       </c>
-      <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11564,7 +11440,6 @@
       <c r="G183" t="n">
         <v>124</v>
       </c>
-      <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11621,7 +11496,6 @@
       <c r="G184" t="n">
         <v>124</v>
       </c>
-      <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11678,7 +11552,6 @@
       <c r="G185" t="n">
         <v>123</v>
       </c>
-      <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11735,7 +11608,6 @@
       <c r="G186" t="n">
         <v>123</v>
       </c>
-      <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11792,7 +11664,6 @@
       <c r="G187" t="n">
         <v>124</v>
       </c>
-      <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11849,7 +11720,6 @@
       <c r="G188" t="n">
         <v>124</v>
       </c>
-      <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11906,7 +11776,6 @@
       <c r="G189" t="n">
         <v>137</v>
       </c>
-      <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11963,7 +11832,6 @@
       <c r="G190" t="n">
         <v>136</v>
       </c>
-      <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12020,7 +11888,6 @@
       <c r="G191" t="n">
         <v>144</v>
       </c>
-      <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12077,7 +11944,6 @@
       <c r="G192" t="n">
         <v>136</v>
       </c>
-      <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12134,7 +12000,6 @@
       <c r="G193" t="n">
         <v>144</v>
       </c>
-      <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12191,7 +12056,6 @@
       <c r="G194" t="n">
         <v>123</v>
       </c>
-      <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12248,7 +12112,6 @@
       <c r="G195" t="n">
         <v>123</v>
       </c>
-      <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12305,7 +12168,6 @@
       <c r="G196" t="n">
         <v>124</v>
       </c>
-      <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12362,7 +12224,6 @@
       <c r="G197" t="n">
         <v>124</v>
       </c>
-      <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12419,7 +12280,6 @@
       <c r="G198" t="n">
         <v>123</v>
       </c>
-      <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12476,7 +12336,6 @@
       <c r="G199" t="n">
         <v>124</v>
       </c>
-      <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12533,7 +12392,6 @@
       <c r="G200" t="n">
         <v>136</v>
       </c>
-      <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12590,7 +12448,6 @@
       <c r="G201" t="n">
         <v>136</v>
       </c>
-      <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12647,7 +12504,6 @@
       <c r="G202" t="n">
         <v>144</v>
       </c>
-      <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12704,7 +12560,6 @@
       <c r="G203" t="n">
         <v>136</v>
       </c>
-      <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12761,7 +12616,6 @@
       <c r="G204" t="n">
         <v>144</v>
       </c>
-      <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12818,7 +12672,6 @@
       <c r="G205" t="n">
         <v>124</v>
       </c>
-      <c r="H205" t="inlineStr"/>
       <c r="I205" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12875,7 +12728,6 @@
       <c r="G206" t="n">
         <v>136</v>
       </c>
-      <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12932,7 +12784,6 @@
       <c r="G207" t="n">
         <v>123</v>
       </c>
-      <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12989,7 +12840,6 @@
       <c r="G208" t="n">
         <v>123</v>
       </c>
-      <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13046,7 +12896,6 @@
       <c r="G209" t="n">
         <v>124</v>
       </c>
-      <c r="H209" t="inlineStr"/>
       <c r="I209" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13103,7 +12952,6 @@
       <c r="G210" t="n">
         <v>124</v>
       </c>
-      <c r="H210" t="inlineStr"/>
       <c r="I210" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13160,7 +13008,6 @@
       <c r="G211" t="n">
         <v>123</v>
       </c>
-      <c r="H211" t="inlineStr"/>
       <c r="I211" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13217,7 +13064,6 @@
       <c r="G212" t="n">
         <v>123</v>
       </c>
-      <c r="H212" t="inlineStr"/>
       <c r="I212" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13274,7 +13120,6 @@
       <c r="G213" t="n">
         <v>124</v>
       </c>
-      <c r="H213" t="inlineStr"/>
       <c r="I213" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13331,7 +13176,6 @@
       <c r="G214" t="n">
         <v>124</v>
       </c>
-      <c r="H214" t="inlineStr"/>
       <c r="I214" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13388,7 +13232,6 @@
       <c r="G215" t="n">
         <v>136</v>
       </c>
-      <c r="H215" t="inlineStr"/>
       <c r="I215" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13445,7 +13288,6 @@
       <c r="G216" t="n">
         <v>136</v>
       </c>
-      <c r="H216" t="inlineStr"/>
       <c r="I216" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13502,7 +13344,6 @@
       <c r="G217" t="n">
         <v>144</v>
       </c>
-      <c r="H217" t="inlineStr"/>
       <c r="I217" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13559,7 +13400,6 @@
       <c r="G218" t="n">
         <v>144</v>
       </c>
-      <c r="H218" t="inlineStr"/>
       <c r="I218" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13616,7 +13456,6 @@
       <c r="G219" t="n">
         <v>129</v>
       </c>
-      <c r="H219" t="inlineStr"/>
       <c r="I219" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13673,7 +13512,6 @@
       <c r="G220" t="n">
         <v>137</v>
       </c>
-      <c r="H220" t="inlineStr"/>
       <c r="I220" t="inlineStr">
         <is>
           <t>Landscape</t>
